--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E2">
         <v>25</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>0</v>
